--- a/data/xlsx/bmet--it-support-service.xlsx
+++ b/data/xlsx/bmet--it-support-service.xlsx
@@ -648,7 +648,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>8</v>
       </c>
@@ -670,7 +672,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>6</v>
       </c>
@@ -692,7 +696,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -715,7 +721,9 @@
       <c r="C19" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>10</v>
       </c>
@@ -738,7 +746,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>7</v>
       </c>
@@ -760,7 +770,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>9</v>
       </c>
@@ -786,7 +798,9 @@
       <c r="C22" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>8</v>
       </c>
@@ -812,7 +826,9 @@
       <c r="C23" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -838,7 +854,9 @@
       <c r="C24" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>4</v>
       </c>
@@ -860,7 +878,9 @@
       <c r="C25" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>3</v>
       </c>
@@ -882,7 +902,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>8</v>
       </c>
